--- a/data/Mörel-Filet/investment_decision/Breiten_MFH_until_2004_investment_decision.xlsx
+++ b/data/Mörel-Filet/investment_decision/Breiten_MFH_until_2004_investment_decision.xlsx
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>45.14239756434365</v>
+        <v>35.02938739437162</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>22520.99249126438</v>
       </c>
       <c r="F2" t="n">
-        <v>50.72924339716408</v>
+        <v>32.72137322060053</v>
       </c>
       <c r="G2" t="n">
         <v>22520.99249126438</v>
       </c>
       <c r="H2" t="n">
-        <v>51.11212565333332</v>
+        <v>32.72137322060054</v>
       </c>
       <c r="I2" t="n">
         <v>22520.99249126438</v>
       </c>
       <c r="J2" t="n">
-        <v>45.14239756434368</v>
+        <v>35.02938739437158</v>
       </c>
       <c r="K2" t="n">
         <v>22520.99249126438</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>64.43819785164395</v>
+        <v>42.6344061259657</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>22520.99249126438</v>
       </c>
       <c r="F3" t="n">
-        <v>64.93967759194307</v>
+        <v>41.02659882797796</v>
       </c>
       <c r="G3" t="n">
         <v>22520.99249126438</v>
       </c>
       <c r="H3" t="n">
-        <v>66.14510378666665</v>
+        <v>41.02659882797801</v>
       </c>
       <c r="I3" t="n">
         <v>22520.99249126438</v>
       </c>
       <c r="J3" t="n">
-        <v>64.43819785164402</v>
+        <v>41.04123165207348</v>
       </c>
       <c r="K3" t="n">
         <v>22520.99249126438</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>65.411408401258</v>
+        <v>57.47203465624792</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>22520.99249126438</v>
       </c>
       <c r="F4" t="n">
-        <v>66.46178012396363</v>
+        <v>54.77084030398819</v>
       </c>
       <c r="G4" t="n">
         <v>22520.99249126438</v>
       </c>
       <c r="H4" t="n">
-        <v>67.00875036961308</v>
+        <v>54.77084030398817</v>
       </c>
       <c r="I4" t="n">
         <v>22520.99249126438</v>
       </c>
       <c r="J4" t="n">
-        <v>66.46178012396363</v>
+        <v>54.7708403039881</v>
       </c>
       <c r="K4" t="n">
         <v>22520.99249126438</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>70.3014939701974</v>
+        <v>61.84415202061531</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>22520.99249126438</v>
       </c>
       <c r="F5" t="n">
-        <v>70.3014939701974</v>
+        <v>61.84415202061551</v>
       </c>
       <c r="G5" t="n">
         <v>22520.99249126438</v>
       </c>
       <c r="H5" t="n">
-        <v>70.3014939701974</v>
+        <v>61.84764687961081</v>
       </c>
       <c r="I5" t="n">
         <v>22520.99249126438</v>
       </c>
       <c r="J5" t="n">
-        <v>70.3014939701974</v>
+        <v>61.8441520206153</v>
       </c>
       <c r="K5" t="n">
         <v>22520.99249126438</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>70.3014939701974</v>
+        <v>63.71855859555501</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>22520.99249126438</v>
       </c>
       <c r="F6" t="n">
-        <v>70.3014939701974</v>
+        <v>63.718558595555</v>
       </c>
       <c r="G6" t="n">
         <v>22520.99249126438</v>
       </c>
       <c r="H6" t="n">
-        <v>70.3014939701974</v>
+        <v>63.68149078769579</v>
       </c>
       <c r="I6" t="n">
         <v>22520.99249126438</v>
       </c>
       <c r="J6" t="n">
-        <v>70.3014939701974</v>
+        <v>63.69203895887313</v>
       </c>
       <c r="K6" t="n">
         <v>22520.99249126438</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Breiten_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Breiten_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>33.78148873689657</v>
+        <v>36.543</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>33.78148873689657</v>
+        <v>36.543</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>19.39848109377743</v>
+        <v>20.9842348906211</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>19.39848109377743</v>
+        <v>20.9842348906211</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Breiten_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Breiten_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>33.78148873689657</v>
+        <v>36.543</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>33.78148873689657</v>
+        <v>36.543</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>25.08596537214812</v>
+        <v>27.13664988935669</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>25.08596537214812</v>
+        <v>27.13664988935669</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Breiten_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Breiten_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>33.78148873689657</v>
+        <v>36.543</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>33.78148873689657</v>
+        <v>36.543</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>27.61884583966242</v>
+        <v>29.87658392972008</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>27.61884583966242</v>
+        <v>29.87658392972008</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Breiten_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Breiten_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>33.78148873689657</v>
+        <v>36.543</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>33.78148873689657</v>
+        <v>36.543</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>29.00679824331515</v>
+        <v>31.37799628847396</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>29.00679824331515</v>
+        <v>31.37799628847396</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Breiten_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Breiten_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>33.78148873689657</v>
+        <v>36.543</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>33.78148873689657</v>
+        <v>36.543</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>29.8685544295388</v>
+        <v>32.31019784295358</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>29.8685544295388</v>
+        <v>32.31019784295358</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.006366908385882354</v>
+        <v>0.005836332687058824</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.006366908385882354</v>
+        <v>0.005836332687058824</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.006366908385882354</v>
+        <v>0.005836332687058824</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.006366908385882354</v>
+        <v>0.005836332687058824</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.006374622422656878</v>
+        <v>0.005836332687058824</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.006632196235294117</v>
+        <v>0.005836332687058824</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.006632196235294117</v>
+        <v>0.005836332687058824</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.006374622422656883</v>
+        <v>0.005836332687058824</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.006374622422656878</v>
+        <v>0.005836332687058824</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.006632196235294117</v>
+        <v>0.005836332687058824</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.006632196235294117</v>
+        <v>0.005836332687058824</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.006374622422656883</v>
+        <v>0.005836332687058824</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.007143003792296444</v>
+        <v>0.005836332687058824</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.007144388091422172</v>
+        <v>0.005836332687058824</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.007140808473110788</v>
+        <v>0.005836332687058824</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.007139612542894089</v>
+        <v>0.005836332687058824</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.007143003792296444</v>
+        <v>0.005836332687058824</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.007144388091422172</v>
+        <v>0.005836332687058824</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.007140808473110788</v>
+        <v>0.005836332687058824</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.007139612542894089</v>
+        <v>0.005836332687058824</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1050,7 +1050,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.08374088559270673</v>
+        <v>0.2959857114132665</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1064,19 +1064,19 @@
         <v>0.9470776224</v>
       </c>
       <c r="F17" t="n">
-        <v>0.05637366800000012</v>
+        <v>0.3030034195784178</v>
       </c>
       <c r="G17" t="n">
         <v>0.9470776224</v>
       </c>
       <c r="H17" t="n">
-        <v>0.05637366800000012</v>
+        <v>0.3030034195784177</v>
       </c>
       <c r="I17" t="n">
         <v>0.9470776224</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08374088559270643</v>
+        <v>0.2959857114132666</v>
       </c>
       <c r="K17" t="n">
         <v>0.9470776224</v>
@@ -1087,7 +1087,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.08374088559270673</v>
+        <v>0.3196309022073985</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         <v>0.9470776224</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05637366800000012</v>
+        <v>0.3253204653086199</v>
       </c>
       <c r="G18" t="n">
         <v>0.9470776224</v>
       </c>
       <c r="H18" t="n">
-        <v>0.05637366800000012</v>
+        <v>0.3241806054819776</v>
       </c>
       <c r="I18" t="n">
         <v>0.9470776224</v>
       </c>
       <c r="J18" t="n">
-        <v>0.08374088559270643</v>
+        <v>0.3244064404810701</v>
       </c>
       <c r="K18" t="n">
         <v>0.9470776224</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.08374088559270673</v>
+        <v>0.3196309022073985</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>0.9470776224</v>
       </c>
       <c r="F19" t="n">
-        <v>0.05637366800000012</v>
+        <v>0.3253204653086199</v>
       </c>
       <c r="G19" t="n">
         <v>0.9470776224</v>
       </c>
       <c r="H19" t="n">
-        <v>0.05637366800000012</v>
+        <v>0.3241806054819776</v>
       </c>
       <c r="I19" t="n">
         <v>0.9470776224</v>
       </c>
       <c r="J19" t="n">
-        <v>0.08374088559270643</v>
+        <v>0.3244064404810701</v>
       </c>
       <c r="K19" t="n">
         <v>0.9470776224</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.002100365068502879</v>
+        <v>0.2565296120127077</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>0.9470776224</v>
       </c>
       <c r="F20" t="n">
-        <v>0.001953283286394404</v>
+        <v>0.2556321908756419</v>
       </c>
       <c r="G20" t="n">
         <v>0.9470776224</v>
       </c>
       <c r="H20" t="n">
-        <v>0.002333617731978766</v>
+        <v>0.2454442236796369</v>
       </c>
       <c r="I20" t="n">
         <v>0.9470776224</v>
       </c>
       <c r="J20" t="n">
-        <v>0.002460685317503184</v>
+        <v>0.2429312375381279</v>
       </c>
       <c r="K20" t="n">
         <v>0.9470776224</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.002100365068502879</v>
+        <v>0.2328844212185758</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>0.9470776224</v>
       </c>
       <c r="F21" t="n">
-        <v>0.001953283286394404</v>
+        <v>0.2333151451454397</v>
       </c>
       <c r="G21" t="n">
         <v>0.9470776224</v>
       </c>
       <c r="H21" t="n">
-        <v>0.002333617731978766</v>
+        <v>0.224267037776077</v>
       </c>
       <c r="I21" t="n">
         <v>0.9470776224</v>
       </c>
       <c r="J21" t="n">
-        <v>0.002460685317503184</v>
+        <v>0.2145105084703245</v>
       </c>
       <c r="K21" t="n">
         <v>0.9470776224</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.01711010977877589</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>0.9470776224</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.0180075309158414</v>
       </c>
       <c r="G30" t="n">
         <v>0.9470776224</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.028186834</v>
       </c>
       <c r="I30" t="n">
         <v>0.9470776224</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.03060829110712121</v>
       </c>
       <c r="K30" t="n">
         <v>0.9470776224</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.03610845552634388</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>0.9470776224</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.03570063348908181</v>
       </c>
       <c r="G31" t="n">
         <v>0.9470776224</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.04481773384460785</v>
       </c>
       <c r="I31" t="n">
         <v>0.9470776224</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.05454811315833576</v>
       </c>
       <c r="K31" t="n">
         <v>0.9470776224</v>
@@ -2345,7 +2345,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>1.95072222575917</v>
+        <v>1.995484454847246</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2359,19 +2359,19 @@
         <v>7.022987744644131</v>
       </c>
       <c r="F52" t="n">
-        <v>1.746365691488268</v>
+        <v>1.717650316151425</v>
       </c>
       <c r="G52" t="n">
         <v>7.022987744644131</v>
       </c>
       <c r="H52" t="n">
-        <v>1.967520111371388</v>
+        <v>1.708173245533427</v>
       </c>
       <c r="I52" t="n">
         <v>1.892207430828986</v>
       </c>
       <c r="J52" t="n">
-        <v>1.995503211788527</v>
+        <v>1.973931502814269</v>
       </c>
       <c r="K52" t="n">
         <v>1.892207430828986</v>
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>2.074117817362731</v>
+        <v>2.158317389964738</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
         <v>7.022987744644131</v>
       </c>
       <c r="F53" t="n">
-        <v>1.893598936650523</v>
+        <v>1.918508199546373</v>
       </c>
       <c r="G53" t="n">
         <v>7.022987744644131</v>
       </c>
       <c r="H53" t="n">
-        <v>2.11089768182167</v>
+        <v>1.909031128928376</v>
       </c>
       <c r="I53" t="n">
         <v>2.791514881406229</v>
       </c>
       <c r="J53" t="n">
-        <v>2.118898803392088</v>
+        <v>2.136126352528551</v>
       </c>
       <c r="K53" t="n">
         <v>2.791514881406229</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>2.225546115688227</v>
+        <v>2.209308494858645</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>7.022987744644131</v>
       </c>
       <c r="F54" t="n">
-        <v>1.981981216804247</v>
+        <v>1.970235683332713</v>
       </c>
       <c r="G54" t="n">
         <v>7.022987744644131</v>
       </c>
       <c r="H54" t="n">
-        <v>2.181988454121978</v>
+        <v>1.960758612714715</v>
       </c>
       <c r="I54" t="n">
         <v>3.30712678964979</v>
       </c>
       <c r="J54" t="n">
-        <v>2.255723881585445</v>
+        <v>2.187755542825667</v>
       </c>
       <c r="K54" t="n">
         <v>3.30712678964979</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>2.42320997716572</v>
+        <v>2.406958877089963</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>7.022987744644131</v>
       </c>
       <c r="F55" t="n">
-        <v>2.393445719623286</v>
+        <v>2.382831623076016</v>
       </c>
       <c r="G55" t="n">
         <v>7.022987744644131</v>
       </c>
       <c r="H55" t="n">
-        <v>2.393445719623286</v>
+        <v>2.382798847242166</v>
       </c>
       <c r="I55" t="n">
         <v>3.638874625821451</v>
       </c>
       <c r="J55" t="n">
-        <v>2.42320997716572</v>
+        <v>2.401364461880975</v>
       </c>
       <c r="K55" t="n">
         <v>3.638874625821451</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>2.422984902868908</v>
+        <v>2.379762067386384</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>7.022987744644131</v>
       </c>
       <c r="F56" t="n">
-        <v>2.343349287282227</v>
+        <v>2.260009183938147</v>
       </c>
       <c r="G56" t="n">
         <v>7.022987744644131</v>
       </c>
       <c r="H56" t="n">
-        <v>2.343367306528224</v>
+        <v>2.260689317462476</v>
       </c>
       <c r="I56" t="n">
         <v>3.86948547069052</v>
       </c>
       <c r="J56" t="n">
-        <v>2.423114755422176</v>
+        <v>2.380695281043108</v>
       </c>
       <c r="K56" t="n">
         <v>3.86948547069052</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.8440097772231888</v>
+        <v>0.3434420846926978</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>7.022987744644131</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9044828642274294</v>
+        <v>0.3570263684957218</v>
       </c>
       <c r="G64" t="n">
         <v>7.022987744644131</v>
       </c>
       <c r="H64" t="n">
-        <v>0.9248608843421303</v>
+        <v>0.3570263684957219</v>
       </c>
       <c r="I64" t="n">
         <v>7.022987744644131</v>
       </c>
       <c r="J64" t="n">
-        <v>0.8536893799051456</v>
+        <v>0.3570263684957226</v>
       </c>
       <c r="K64" t="n">
         <v>7.022987744644131</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.9553239124364171</v>
+        <v>0.3514319532867349</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>7.022987744644131</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9850881699788516</v>
+        <v>0.3755592073006814</v>
       </c>
       <c r="G65" t="n">
         <v>7.022987744644131</v>
       </c>
       <c r="H65" t="n">
-        <v>0.9850881699788508</v>
+        <v>0.3755744075178761</v>
       </c>
       <c r="I65" t="n">
         <v>7.022987744644131</v>
       </c>
       <c r="J65" t="n">
-        <v>0.9553239124364171</v>
+        <v>0.3570263684957226</v>
       </c>
       <c r="K65" t="n">
         <v>7.022987744644131</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>1.378208538927517</v>
+        <v>0.6223425816665513</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>7.022987744644131</v>
       </c>
       <c r="F66" t="n">
-        <v>1.457844154514198</v>
+        <v>0.7420954651147884</v>
       </c>
       <c r="G66" t="n">
         <v>7.022987744644131</v>
       </c>
       <c r="H66" t="n">
-        <v>1.457826135268201</v>
+        <v>0.7416819064089208</v>
       </c>
       <c r="I66" t="n">
         <v>7.022987744644131</v>
       </c>
       <c r="J66" t="n">
-        <v>1.378078686374248</v>
+        <v>0.6216000851776988</v>
       </c>
       <c r="K66" t="n">
         <v>7.022987744644131</v>
@@ -3108,13 +3108,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2131847398021909</v>
+        <v>7.022987744644131</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.2131847398021909</v>
+        <v>7.022987744644131</v>
       </c>
     </row>
     <row r="73">
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3610538337293448</v>
+        <v>7.022987744644131</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.3610538337293448</v>
+        <v>7.022987744644131</v>
       </c>
     </row>
     <row r="74">
@@ -3182,13 +3182,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4753202330494226</v>
+        <v>7.022987744644131</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.4753202330494226</v>
+        <v>7.022987744644131</v>
       </c>
     </row>
     <row r="75">
@@ -3219,13 +3219,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5682189894126216</v>
+        <v>7.022987744644131</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.5682189894126216</v>
+        <v>7.022987744644131</v>
       </c>
     </row>
     <row r="76">
@@ -3256,13 +3256,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0.646195005730167</v>
+        <v>7.022987744644131</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.646195005730167</v>
+        <v>7.022987744644131</v>
       </c>
     </row>
     <row r="77">
@@ -3270,7 +3270,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0.3319002727951246</v>
+        <v>0.227627592479616</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3284,22 +3284,22 @@
         <v>7.022987744644131</v>
       </c>
       <c r="F77" t="n">
-        <v>0.5100684672246807</v>
+        <v>0.4667004040055484</v>
       </c>
       <c r="G77" t="n">
         <v>7.022987744644131</v>
       </c>
       <c r="H77" t="n">
-        <v>0.2871192867657679</v>
+        <v>0.4761774746235461</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2131847398021909</v>
+        <v>7.022987744644131</v>
       </c>
       <c r="J77" t="n">
-        <v>0.2871192867657679</v>
+        <v>0.2491805445125939</v>
       </c>
       <c r="K77" t="n">
-        <v>0.2131847398021909</v>
+        <v>7.022987744644131</v>
       </c>
     </row>
     <row r="78">
@@ -3307,7 +3307,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.3319002727951246</v>
+        <v>0.227627592479616</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3321,22 +3321,22 @@
         <v>7.022987744644131</v>
       </c>
       <c r="F78" t="n">
-        <v>0.5100684672246807</v>
+        <v>0.4667004040055484</v>
       </c>
       <c r="G78" t="n">
         <v>7.022987744644131</v>
       </c>
       <c r="H78" t="n">
-        <v>0.2871192867657679</v>
+        <v>0.4761774746235461</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3610538337293448</v>
+        <v>7.022987744644131</v>
       </c>
       <c r="J78" t="n">
-        <v>0.2871192867657679</v>
+        <v>0.2491805445125939</v>
       </c>
       <c r="K78" t="n">
-        <v>0.3610538337293448</v>
+        <v>7.022987744644131</v>
       </c>
     </row>
     <row r="79">
@@ -3344,7 +3344,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.3319002727951246</v>
+        <v>0.227627592479616</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3358,22 +3358,22 @@
         <v>7.022987744644131</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5100684672246807</v>
+        <v>0.4667004040055484</v>
       </c>
       <c r="G79" t="n">
         <v>7.022987744644131</v>
       </c>
       <c r="H79" t="n">
-        <v>0.2871192867657679</v>
+        <v>0.4761774746235462</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4753202330494226</v>
+        <v>7.022987744644131</v>
       </c>
       <c r="J79" t="n">
-        <v>0.2871192867657679</v>
+        <v>0.2491805445125939</v>
       </c>
       <c r="K79" t="n">
-        <v>0.4753202330494226</v>
+        <v>7.022987744644131</v>
       </c>
     </row>
     <row r="80">
@@ -3404,13 +3404,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0.5682189894126216</v>
+        <v>7.022987744644131</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.5682189894126216</v>
+        <v>7.022987744644131</v>
       </c>
     </row>
     <row r="81">
@@ -3441,13 +3441,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0.646195005730167</v>
+        <v>7.022987744644131</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.646195005730167</v>
+        <v>7.022987744644131</v>
       </c>
     </row>
     <row r="82">
